--- a/src/main/resources/config.xlsx
+++ b/src/main/resources/config.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10315"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10714"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/abhisheksharma/Desktop/Selenium Templets/3_SOCIALSERVICE/PL2-22 TCs/VM-Java-Health-App_Social-Service-Automation-PL2-Selenium_Excel-Solution-22TCs/src/main/resources/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/abhisheksharma/Documents/Health App WS/HealthApp_Dispensary_L2/src/main/resources/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7C6F66EF-DCCF-924B-A648-0F7C30142021}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{CEA7E678-E533-A446-9604-020371A1F0C7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="1480" yWindow="1740" windowWidth="27240" windowHeight="16260" activeTab="1" xr2:uid="{B1958625-4DE1-E940-957A-F4129650B306}"/>
   </bookViews>
@@ -478,8 +478,7 @@
   <dimension ref="A1:B3"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="14.83203125" style="1" bestFit="1" customWidth="1"/>
-    <col min="2" max="16384" width="10.83203125" style="1"/>
+    <col min="1" max="16384" width="10.83203125" style="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:2" x14ac:dyDescent="0.2">
